--- a/output/pdf_financials_xlsx/TTGI.xlsx
+++ b/output/pdf_financials_xlsx/TTGI.xlsx
@@ -3420,25 +3420,25 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06983300000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06983300000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.119747</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.693161</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.703814</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.381186</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.867191</v>
       </c>
     </row>
     <row r="93">
@@ -6502,7 +6502,11 @@
           <t>Warrant reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -6556,7 +6560,11 @@
           <t>Share-based payment reserve (Note 17)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -7400,7 +7408,11 @@
           <t>Warrant reserve (Note 17)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -7452,7 +7464,11 @@
           <t>Share-based payment reserve (Notes 17 and 18)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -8174,7 +8190,11 @@
           <t>Share-based payment reserve (Notes 16 and 17)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -8852,7 +8872,11 @@
           <t>Share-based payment reserve (Notes 15 and 16)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -9252,7 +9276,11 @@
           <t>Reserves 7,8</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -9584,7 +9612,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TTGI.xlsx
+++ b/output/pdf_financials_xlsx/TTGI.xlsx
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.408647</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.133757</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.432346</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.608969</v>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.408647</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.133757</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.432346</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.608969</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.469214</v>
+        <v>0.036868</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.16651</v>
@@ -4510,19 +4510,19 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025096</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.051651</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-1.85</v>
+        <v>-0.220484</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.219788</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.223203</v>
       </c>
     </row>
     <row r="125">
@@ -4545,19 +4545,19 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025096</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.051651</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-3.7</v>
+        <v>-2.070484</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0.55</v>
+        <v>0.330212</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.223203</v>
       </c>
     </row>
     <row r="126">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11574,7 +11574,11 @@
           <t>Lease payments (Note 10)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -15020,7 +15024,11 @@
           <t>Lease payments (Note 11)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -16888,7 +16896,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TTGI.xlsx
+++ b/output/pdf_financials_xlsx/TTGI.xlsx
@@ -923,7 +923,7 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.08019</v>
+        <v>-0.08019</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -932,7 +932,7 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.07956100000000001</v>
+        <v>-0.08477999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.860867</v>
@@ -1410,7 +1410,7 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-2.637975561565749</v>
+        <v>-2.811020074025518</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-8.255442721199493</v>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.123294</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.160931</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.000185</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.106487</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.167411</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.166352</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.176167</v>
       </c>
     </row>
     <row r="71">
@@ -2724,16 +2724,16 @@
         <v>1.281558</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.002268</v>
+        <v>2.108755</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.819029</v>
+        <v>0.98644</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>5.310805</v>
+        <v>5.477157</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>8.065566</v>
+        <v>8.241733</v>
       </c>
     </row>
     <row r="72">
@@ -2856,10 +2856,10 @@
         <v>0.21337</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.44009</v>
+        <v>0.333603</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.443951</v>
+        <v>0.27654</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0</v>
@@ -3029,16 +3029,16 @@
         <v>-0.4304155513536569</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>-1.680904378270599</v>
+        <v>-1.749640302629906</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-1.154153132953072</v>
+        <v>-1.294952254235891</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>-27.69845454049956</v>
+        <v>-28.52272603398128</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.8118545977755235</v>
+        <v>-0.8293645326983252</v>
       </c>
     </row>
     <row r="81">
@@ -4018,19 +4018,19 @@
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.080719</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.887923</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.128271</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.302983</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>1.307601</v>
       </c>
     </row>
     <row r="111">
@@ -4062,10 +4062,10 @@
         <v>-0.005235</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003601</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006597</v>
       </c>
     </row>
     <row r="112">
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.26732</v>
       </c>
     </row>
     <row r="117">
@@ -4881,10 +4881,10 @@
         <v>-0.005235</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003601</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006597</v>
       </c>
     </row>
     <row r="135">
@@ -4918,10 +4918,10 @@
         <v>-2.615241</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.520723</v>
+        <v>-1.524324</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.883214</v>
+        <v>-3.889811</v>
       </c>
     </row>
   </sheetData>
@@ -5896,7 +5896,11 @@
           <t>Lease liabilities (Note 10)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8078,7 +8082,11 @@
           <t>Lease liabilities (Note 11)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -9996,7 +10004,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -11136,7 +11148,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -11188,7 +11204,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -12182,7 +12202,11 @@
           <t>Accretion (Notes 12 and 23)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -14022,7 +14046,11 @@
           <t>Accretion (Note 12, 23)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -17362,7 +17390,11 @@
           <t>Shares issued for cash -</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E223" s="5" t="n">
         <v>0.643577</v>
       </c>
@@ -19154,7 +19186,11 @@
           <t>Deferred income tax recovery (Note 28)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -21518,7 +21554,11 @@
           <t>Deferred Income tax recovery (Note 26)</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -23536,7 +23576,11 @@
           <t>Deferred income tax recovery (Note 26)</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -25762,7 +25806,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
